--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -39592,7 +39592,7 @@
       </c>
       <c r="I547" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="J547" s="2" t="inlineStr"/>
@@ -39608,12 +39608,12 @@
       </c>
       <c r="Q547" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>人による試聴結果（2026-09-25、ユーザー提供）：A判定済み21曲を実際に試聴し、全曲の用途候補・曲調・長時間BGM適性・ループ評価・所見を記録した。試聴は人が実施したものであり、Codexは試聴していない。</t>
         </is>
       </c>
       <c r="R547" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S547" s="2" t="inlineStr">
@@ -48795,7 +48795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51301,12 +51301,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01545</t>
+          <t>WBS-001-01546</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>確認対象曲を試聴して用途・曲調を評価する</t>
+          <t>人の試聴結果と配布元情報を基に用途・曲調を曲単位で整理する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -51328,24 +51328,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01545.md</t>
+          <t>wbs/tasks/WBS-001-01546.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01546</t>
+          <t>WBS-001-01547</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>人の試聴結果と配布元情報を基に用途・曲調を曲単位で整理する</t>
+          <t>作者・配布元・ライセンス・形式・用途・曲調の分布を再集計する</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -51362,19 +51362,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01546.md</t>
+          <t>wbs/tasks/WBS-001-01547.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01547</t>
+          <t>WBS-001-01548</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>作者・配布元・ライセンス・形式・用途・曲調の分布を再集計する</t>
+          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51396,19 +51396,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01547.md</t>
+          <t>wbs/tasks/WBS-001-01548.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01548</t>
+          <t>WBS-001-01549</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
+          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51430,19 +51430,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01548.md</t>
+          <t>wbs/tasks/WBS-001-01549.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01549</t>
+          <t>WBS-001-01556</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51452,7 +51452,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01528</t>
+          <t>WBS-001-01525</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -51464,19 +51464,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01549.md</t>
+          <t>wbs/tasks/WBS-001-01556.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01558</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51486,7 +51486,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01525</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -51498,19 +51498,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01556.md</t>
+          <t>wbs/tasks/WBS-001-01558.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01558</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>CH1～CH4の役割と発音密度を整理する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51532,19 +51532,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01558.md</t>
+          <t>wbs/tasks/WBS-001-01559.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51566,19 +51566,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01559.md</t>
+          <t>wbs/tasks/WBS-001-01560.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01561</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>motifの反復・変奏パターンを整理する</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51600,19 +51600,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01560.md</t>
+          <t>wbs/tasks/WBS-001-01561.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01561</t>
+          <t>WBS-001-01562</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>CH2の伴奏パターンを整理する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51634,19 +51634,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01561.md</t>
+          <t>wbs/tasks/WBS-001-01562.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01562</t>
+          <t>WBS-001-01563</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>CH3のベースパターンを整理する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51668,19 +51668,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01562.md</t>
+          <t>wbs/tasks/WBS-001-01563.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01563</t>
+          <t>WBS-001-01564</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>CH4のリズムパターンを整理する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -51702,19 +51702,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01563.md</t>
+          <t>wbs/tasks/WBS-001-01564.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01564</t>
+          <t>WBS-001-01565</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51736,19 +51736,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01564.md</t>
+          <t>wbs/tasks/WBS-001-01565.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01565</t>
+          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
+          <t>WBS-001-01566</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -51770,19 +51770,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01565.md</t>
+          <t>wbs/tasks/WBS-001-01567.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01567</t>
+          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>解析結果を共通の中間表現へ変換する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51804,19 +51804,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01568</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>曲・pattern・channel単位の特徴を自動出力する</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51838,19 +51838,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01570</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -51872,19 +51872,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>ハードウェア制約に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -51894,7 +51894,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
+          <t>WBS-001-01571</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -51906,19 +51906,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>一般的な音楽理論に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -51940,19 +51940,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -51974,19 +51974,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>各ルールに根拠を記録できる形式を決める</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -52008,19 +52008,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01576</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52042,19 +52042,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01577</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52076,19 +52076,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52098,7 +52098,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -52110,19 +52110,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01580</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
+          <t>曲構成とloop構造を生成する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52144,19 +52144,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01581</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -52178,19 +52178,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -52212,19 +52212,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52246,19 +52246,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52280,19 +52280,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -52314,19 +52314,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -52336,7 +52336,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
+          <t>WBS-001-01586</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -52348,19 +52348,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01587</t>
+          <t>WBS-001-01588</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
+          <t>hUGEDriver用ASMを生成する</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -52382,19 +52382,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01589</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>hUGEDriver用ASMを生成する</t>
+          <t>確認用ROMを生成する</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -52416,19 +52416,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -52450,19 +52450,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -52484,19 +52484,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01591</t>
+          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
+          <t>複数seedで候補曲を生成する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -52506,7 +52506,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
+          <t>WBS-001-01592</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -52518,24 +52518,24 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01593</t>
+          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>複数seedで候補曲を生成する</t>
+          <t>人がSameBoyで候補曲を試聴する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -52552,24 +52552,24 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01594</t>
+          <t>WBS-001-01595</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
+          <t>実用候補となるBGMが生成できるか確認する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -52586,19 +52586,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01595</t>
+          <t>WBS-001-01596</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
+          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52620,19 +52620,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01597</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -52654,19 +52654,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -52688,19 +52688,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52710,7 +52710,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -52722,19 +52722,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -52756,19 +52756,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -52790,19 +52790,19 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -52824,24 +52824,24 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -52858,29 +52858,29 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -52892,19 +52892,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -52926,19 +52926,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -52960,19 +52960,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -52994,19 +52994,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53062,19 +53062,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53096,19 +53096,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53130,19 +53130,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53152,7 +53152,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -53164,19 +53164,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53198,19 +53198,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53232,19 +53232,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53266,19 +53266,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53300,19 +53300,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53334,19 +53334,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53368,19 +53368,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -53436,19 +53436,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -53470,19 +53470,19 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -53504,19 +53504,19 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -53538,19 +53538,19 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -53560,7 +53560,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -53572,24 +53572,24 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -53606,29 +53606,29 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01661</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -53640,46 +53640,12 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H143"/>
+  <autoFilter ref="A1:H142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53747,7 +53713,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53764,7 +53730,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53781,7 +53747,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7446043165467626</v>
+        <v>0.7464028776978417</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53849,7 +53815,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -54179,19 +54145,19 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.820855614973262</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>63</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -74522,7 +74488,7 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F547" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -39663,7 +39663,7 @@
       </c>
       <c r="I548" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="J548" s="2" t="inlineStr"/>
@@ -39679,12 +39679,12 @@
       </c>
       <c r="Q548" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>人による確認結果はWBS-001-01545（2026-09-25）を正本として使用した。配布元情報・実ファイル確認は `docs/game-boy-music-source-candidates.md` の既存記録を使用した。整理結果は本WBS本文と同文書の曲単位整理節に記録した。試聴・採用判断は人が行ったものであり、Codexは試聴していない。</t>
         </is>
       </c>
       <c r="R548" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S548" s="2" t="inlineStr">
@@ -48795,7 +48795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51301,17 +51301,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01546</t>
+          <t>WBS-001-01547</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>人の試聴結果と配布元情報を基に用途・曲調を曲単位で整理する</t>
+          <t>作者・配布元・ライセンス・形式・用途・曲調の分布を再集計する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -51328,19 +51328,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01546.md</t>
+          <t>wbs/tasks/WBS-001-01547.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01547</t>
+          <t>WBS-001-01548</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>作者・配布元・ライセンス・形式・用途・曲調の分布を再集計する</t>
+          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -51362,19 +51362,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01547.md</t>
+          <t>wbs/tasks/WBS-001-01548.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01548</t>
+          <t>WBS-001-01549</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
+          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51396,19 +51396,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01548.md</t>
+          <t>wbs/tasks/WBS-001-01549.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01549</t>
+          <t>WBS-001-01556</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51418,7 +51418,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01528</t>
+          <t>WBS-001-01525</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -51430,19 +51430,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01549.md</t>
+          <t>wbs/tasks/WBS-001-01556.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01558</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51452,7 +51452,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01525</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -51464,19 +51464,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01556.md</t>
+          <t>wbs/tasks/WBS-001-01558.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01558</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>CH1～CH4の役割と発音密度を整理する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51498,19 +51498,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01558.md</t>
+          <t>wbs/tasks/WBS-001-01559.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51532,19 +51532,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01559.md</t>
+          <t>wbs/tasks/WBS-001-01560.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01561</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>motifの反復・変奏パターンを整理する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51566,19 +51566,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01560.md</t>
+          <t>wbs/tasks/WBS-001-01561.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01561</t>
+          <t>WBS-001-01562</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>CH2の伴奏パターンを整理する</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51600,19 +51600,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01561.md</t>
+          <t>wbs/tasks/WBS-001-01562.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01562</t>
+          <t>WBS-001-01563</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>CH3のベースパターンを整理する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51634,19 +51634,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01562.md</t>
+          <t>wbs/tasks/WBS-001-01563.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01563</t>
+          <t>WBS-001-01564</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>CH4のリズムパターンを整理する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51668,19 +51668,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01563.md</t>
+          <t>wbs/tasks/WBS-001-01564.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01564</t>
+          <t>WBS-001-01565</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -51702,19 +51702,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01564.md</t>
+          <t>wbs/tasks/WBS-001-01565.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01565</t>
+          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51724,7 +51724,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
+          <t>WBS-001-01566</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -51736,19 +51736,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01565.md</t>
+          <t>wbs/tasks/WBS-001-01567.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01567</t>
+          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>解析結果を共通の中間表現へ変換する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51770,19 +51770,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01568</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>曲・pattern・channel単位の特徴を自動出力する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51804,19 +51804,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01570</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51838,19 +51838,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>ハードウェア制約に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -51860,7 +51860,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
+          <t>WBS-001-01571</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -51872,19 +51872,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>一般的な音楽理論に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -51906,19 +51906,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -51940,19 +51940,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>各ルールに根拠を記録できる形式を決める</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -51974,19 +51974,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01576</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -52008,19 +52008,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01577</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52042,19 +52042,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52064,7 +52064,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -52076,19 +52076,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01580</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
+          <t>曲構成とloop構造を生成する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52110,19 +52110,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01581</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52144,19 +52144,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -52178,19 +52178,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -52212,19 +52212,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52246,19 +52246,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52280,19 +52280,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -52302,7 +52302,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
+          <t>WBS-001-01586</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -52314,19 +52314,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01587</t>
+          <t>WBS-001-01588</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
+          <t>hUGEDriver用ASMを生成する</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -52348,19 +52348,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01589</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>hUGEDriver用ASMを生成する</t>
+          <t>確認用ROMを生成する</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -52382,19 +52382,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -52416,19 +52416,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -52450,19 +52450,19 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01591</t>
+          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
+          <t>複数seedで候補曲を生成する</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -52472,7 +52472,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
+          <t>WBS-001-01592</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -52484,24 +52484,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01593</t>
+          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>複数seedで候補曲を生成する</t>
+          <t>人がSameBoyで候補曲を試聴する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -52518,24 +52518,24 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01594</t>
+          <t>WBS-001-01595</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
+          <t>実用候補となるBGMが生成できるか確認する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -52552,19 +52552,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01595</t>
+          <t>WBS-001-01596</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
+          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -52586,19 +52586,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01597</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52620,19 +52620,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -52654,19 +52654,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -52676,7 +52676,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -52688,19 +52688,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52722,19 +52722,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -52756,19 +52756,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -52790,24 +52790,24 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -52824,29 +52824,29 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -52858,19 +52858,19 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -52892,19 +52892,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -52926,19 +52926,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -52960,19 +52960,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -52994,19 +52994,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53062,19 +53062,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53096,19 +53096,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53118,7 +53118,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -53130,19 +53130,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53164,19 +53164,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53198,19 +53198,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53232,19 +53232,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53266,19 +53266,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53300,19 +53300,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53334,19 +53334,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53368,19 +53368,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -53436,19 +53436,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -53470,19 +53470,19 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -53504,19 +53504,19 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -53526,7 +53526,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -53538,24 +53538,24 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -53572,29 +53572,29 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01661</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -53606,46 +53606,12 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H142"/>
+  <autoFilter ref="A1:H141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53713,7 +53679,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53730,7 +53696,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53747,7 +53713,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7464028776978417</v>
+        <v>0.7482014388489209</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53815,7 +53781,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -54145,19 +54111,19 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8262032085561497</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>63</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -74525,7 +74491,7 @@
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F548" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$140</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="I549" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="J549" s="2" t="inlineStr"/>
@@ -39750,12 +39750,12 @@
       </c>
       <c r="Q549" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>集計結果と母集団の分母は `docs/game-boy-music-source-candidates.md` の「WBS-001-01547 再集計（2026-09-25）」および「A判定21曲の曲調タグ（人による評価）」に記録した。人による用途・曲調評価の正本はWBS-001-01545/01546であり、Codexは試聴していない。D判定・未判定候補をA判定21曲へ混在させず、WBS-001-01548の不足分析・提案は実施していない。</t>
         </is>
       </c>
       <c r="R549" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S549" s="2" t="inlineStr">
@@ -48795,7 +48795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51301,12 +51301,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01547</t>
+          <t>WBS-001-01548</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>作者・配布元・ライセンス・形式・用途・曲調の分布を再集計する</t>
+          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -51328,19 +51328,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01547.md</t>
+          <t>wbs/tasks/WBS-001-01548.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01548</t>
+          <t>WBS-001-01549</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
+          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -51362,19 +51362,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01548.md</t>
+          <t>wbs/tasks/WBS-001-01549.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01549</t>
+          <t>WBS-001-01556</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51384,7 +51384,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01528</t>
+          <t>WBS-001-01525</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -51396,19 +51396,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01549.md</t>
+          <t>wbs/tasks/WBS-001-01556.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01558</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51418,7 +51418,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01525</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -51430,19 +51430,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01556.md</t>
+          <t>wbs/tasks/WBS-001-01558.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01558</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>CH1～CH4の役割と発音密度を整理する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51464,19 +51464,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01558.md</t>
+          <t>wbs/tasks/WBS-001-01559.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51498,19 +51498,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01559.md</t>
+          <t>wbs/tasks/WBS-001-01560.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01561</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>motifの反復・変奏パターンを整理する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51532,19 +51532,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01560.md</t>
+          <t>wbs/tasks/WBS-001-01561.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01561</t>
+          <t>WBS-001-01562</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>CH2の伴奏パターンを整理する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51566,19 +51566,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01561.md</t>
+          <t>wbs/tasks/WBS-001-01562.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01562</t>
+          <t>WBS-001-01563</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>CH3のベースパターンを整理する</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51600,19 +51600,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01562.md</t>
+          <t>wbs/tasks/WBS-001-01563.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01563</t>
+          <t>WBS-001-01564</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>CH4のリズムパターンを整理する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51634,19 +51634,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01563.md</t>
+          <t>wbs/tasks/WBS-001-01564.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01564</t>
+          <t>WBS-001-01565</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51668,19 +51668,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01564.md</t>
+          <t>wbs/tasks/WBS-001-01565.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01565</t>
+          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -51690,7 +51690,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
+          <t>WBS-001-01566</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -51702,19 +51702,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01565.md</t>
+          <t>wbs/tasks/WBS-001-01567.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01567</t>
+          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>解析結果を共通の中間表現へ変換する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51736,19 +51736,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01568</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>曲・pattern・channel単位の特徴を自動出力する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51770,19 +51770,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01570</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51804,19 +51804,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>ハードウェア制約に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51826,7 +51826,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
+          <t>WBS-001-01571</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -51838,19 +51838,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>一般的な音楽理論に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -51872,19 +51872,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -51906,19 +51906,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>各ルールに根拠を記録できる形式を決める</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -51940,19 +51940,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01576</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -51974,19 +51974,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01577</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -52008,19 +52008,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52030,7 +52030,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -52042,19 +52042,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01580</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
+          <t>曲構成とloop構造を生成する</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52076,19 +52076,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01581</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52110,19 +52110,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52144,19 +52144,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -52178,19 +52178,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -52212,19 +52212,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52246,19 +52246,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52268,7 +52268,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
+          <t>WBS-001-01586</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -52280,19 +52280,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01587</t>
+          <t>WBS-001-01588</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
+          <t>hUGEDriver用ASMを生成する</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -52314,19 +52314,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01589</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>hUGEDriver用ASMを生成する</t>
+          <t>確認用ROMを生成する</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -52348,19 +52348,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -52382,19 +52382,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -52416,19 +52416,19 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01591</t>
+          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
+          <t>複数seedで候補曲を生成する</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -52438,7 +52438,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
+          <t>WBS-001-01592</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -52450,24 +52450,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01593</t>
+          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>複数seedで候補曲を生成する</t>
+          <t>人がSameBoyで候補曲を試聴する</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -52484,24 +52484,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01594</t>
+          <t>WBS-001-01595</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
+          <t>実用候補となるBGMが生成できるか確認する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -52518,19 +52518,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01595</t>
+          <t>WBS-001-01596</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
+          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -52552,19 +52552,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01597</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -52586,19 +52586,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52620,19 +52620,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -52642,7 +52642,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -52654,19 +52654,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -52688,19 +52688,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52722,19 +52722,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -52756,24 +52756,24 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -52790,29 +52790,29 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -52824,19 +52824,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -52858,19 +52858,19 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -52892,19 +52892,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -52926,19 +52926,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -52960,19 +52960,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -52994,19 +52994,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53062,19 +53062,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53084,7 +53084,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -53096,19 +53096,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53130,19 +53130,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53164,19 +53164,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53198,19 +53198,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53232,19 +53232,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53266,19 +53266,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53300,19 +53300,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53334,19 +53334,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53368,19 +53368,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -53436,19 +53436,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -53470,19 +53470,19 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -53492,7 +53492,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -53504,24 +53504,24 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -53538,29 +53538,29 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01661</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -53572,46 +53572,12 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H141"/>
+  <autoFilter ref="A1:H140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53626,7 +53592,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -53679,7 +53645,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53696,7 +53662,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53713,7 +53679,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7482014388489209</v>
+        <v>0.75</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53747,7 +53713,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
@@ -54111,16 +54077,16 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8262032085561497</v>
+        <v>0.8288770053475936</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2</v>
@@ -74528,7 +74494,7 @@
       </c>
       <c r="E549" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F549" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -39805,7 +39805,7 @@
       </c>
       <c r="I550" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="J550" s="2" t="inlineStr"/>
@@ -39816,17 +39816,17 @@
       <c r="O550" s="2" t="inlineStr"/>
       <c r="P550" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>01547の実数を照合し、用途・曲調・作者・ASMの不足または未確保状況を候補数と最終採用数を分けて記録した。lillstrumpa 11曲とhUGEDriver sample ASM保留1件を未確定として記録し、01549を先取りしていない。</t>
         </is>
       </c>
       <c r="Q550" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>不足状況と次に確認すべき条件は `docs/game-boy-music-source-candidates.md` の「WBS-001-01548 不足状況の整理（2026-09-25）」に記録した。数値の根拠は同文書の「WBS-001-01547 再集計」、人による評価の根拠はWBS-001-01545/01546、用途仕様の根拠は `docs/sound-spec.md`、形式・変換条件の根拠は `docs/json-format.md` である。Codexは試聴・採用判断・新規素材探索を行っていない。</t>
         </is>
       </c>
       <c r="R550" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S550" s="2" t="inlineStr">
@@ -48795,7 +48795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51301,12 +51301,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01548</t>
+          <t>WBS-001-01549</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>不足する用途・曲調・作者・ASM候補を実数に基づいて整理する</t>
+          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -51328,19 +51328,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01548.md</t>
+          <t>wbs/tasks/WBS-001-01549.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01549</t>
+          <t>WBS-001-01556</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -51350,7 +51350,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01528</t>
+          <t>WBS-001-01525</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -51362,19 +51362,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01549.md</t>
+          <t>wbs/tasks/WBS-001-01556.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01558</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51384,7 +51384,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01525</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -51396,19 +51396,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01556.md</t>
+          <t>wbs/tasks/WBS-001-01558.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01558</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>CH1～CH4の役割と発音密度を整理する</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51430,19 +51430,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01558.md</t>
+          <t>wbs/tasks/WBS-001-01559.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51464,19 +51464,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01559.md</t>
+          <t>wbs/tasks/WBS-001-01560.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01561</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>motifの反復・変奏パターンを整理する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51498,19 +51498,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01560.md</t>
+          <t>wbs/tasks/WBS-001-01561.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01561</t>
+          <t>WBS-001-01562</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>CH2の伴奏パターンを整理する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51532,19 +51532,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01561.md</t>
+          <t>wbs/tasks/WBS-001-01562.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01562</t>
+          <t>WBS-001-01563</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>CH3のベースパターンを整理する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51566,19 +51566,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01562.md</t>
+          <t>wbs/tasks/WBS-001-01563.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01563</t>
+          <t>WBS-001-01564</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>CH4のリズムパターンを整理する</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51600,19 +51600,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01563.md</t>
+          <t>wbs/tasks/WBS-001-01564.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01564</t>
+          <t>WBS-001-01565</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51634,19 +51634,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01564.md</t>
+          <t>wbs/tasks/WBS-001-01565.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01565</t>
+          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51656,7 +51656,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
+          <t>WBS-001-01566</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -51668,19 +51668,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01565.md</t>
+          <t>wbs/tasks/WBS-001-01567.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01567</t>
+          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>解析結果を共通の中間表現へ変換する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -51702,19 +51702,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01568</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>曲・pattern・channel単位の特徴を自動出力する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51736,19 +51736,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01570</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51770,19 +51770,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>ハードウェア制約に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51792,7 +51792,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
+          <t>WBS-001-01571</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -51804,19 +51804,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>一般的な音楽理論に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51838,19 +51838,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -51872,19 +51872,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>各ルールに根拠を記録できる形式を決める</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -51906,19 +51906,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01576</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -51940,19 +51940,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01577</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -51974,19 +51974,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -51996,7 +51996,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -52008,19 +52008,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01580</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
+          <t>曲構成とloop構造を生成する</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52042,19 +52042,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01581</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52076,19 +52076,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52110,19 +52110,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52144,19 +52144,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -52178,19 +52178,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -52212,19 +52212,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52234,7 +52234,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
+          <t>WBS-001-01586</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -52246,19 +52246,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01587</t>
+          <t>WBS-001-01588</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
+          <t>hUGEDriver用ASMを生成する</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52280,19 +52280,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01589</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>hUGEDriver用ASMを生成する</t>
+          <t>確認用ROMを生成する</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -52314,19 +52314,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -52348,19 +52348,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -52382,19 +52382,19 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01591</t>
+          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
+          <t>複数seedで候補曲を生成する</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -52404,7 +52404,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
+          <t>WBS-001-01592</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -52416,24 +52416,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01593</t>
+          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>複数seedで候補曲を生成する</t>
+          <t>人がSameBoyで候補曲を試聴する</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -52450,24 +52450,24 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01594</t>
+          <t>WBS-001-01595</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
+          <t>実用候補となるBGMが生成できるか確認する</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -52484,19 +52484,19 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01595</t>
+          <t>WBS-001-01596</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
+          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -52518,19 +52518,19 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01597</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -52552,19 +52552,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -52586,19 +52586,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52608,7 +52608,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -52620,19 +52620,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -52654,19 +52654,19 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -52688,19 +52688,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52722,24 +52722,24 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -52756,29 +52756,29 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -52790,19 +52790,19 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -52824,19 +52824,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -52858,19 +52858,19 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -52892,19 +52892,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -52926,19 +52926,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -52960,19 +52960,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -52994,19 +52994,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53050,7 +53050,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -53062,19 +53062,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53096,19 +53096,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53130,19 +53130,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53164,19 +53164,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53198,19 +53198,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53232,19 +53232,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53266,19 +53266,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53300,19 +53300,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53334,19 +53334,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53368,19 +53368,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -53402,19 +53402,19 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -53436,19 +53436,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -53458,7 +53458,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -53470,24 +53470,24 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -53504,29 +53504,29 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01661</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -53538,46 +53538,12 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H140"/>
+  <autoFilter ref="A1:H139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53592,7 +53558,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -53645,7 +53611,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53662,7 +53628,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53679,7 +53645,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.75</v>
+        <v>0.7517985611510791</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53713,7 +53679,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
@@ -54077,16 +54043,16 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8288770053475936</v>
+        <v>0.8315508021390374</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>2</v>
@@ -74531,7 +74497,7 @@
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F550" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -39866,7 +39866,7 @@
       </c>
       <c r="G551" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>解析元コーパスとして利用可能な楽曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="H551" s="2" t="inlineStr">
@@ -39876,10 +39876,14 @@
       </c>
       <c r="I551" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="J551" s="2" t="inlineStr"/>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01547, WBS-001-01548</t>
+        </is>
+      </c>
       <c r="K551" s="2" t="inlineStr"/>
       <c r="L551" s="2" t="inlineStr"/>
       <c r="M551" s="2" t="inlineStr"/>
@@ -39887,17 +39891,17 @@
       <c r="O551" s="2" t="inlineStr"/>
       <c r="P551" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>解析元コーパスをA判定21曲として確認し、採用曲0曲、未確認11曲、保留ASM 1件を混同せず記録する。</t>
         </is>
       </c>
       <c r="Q551" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>WBS-001-01547、WBS-001-01548、docs/game-boy-music-source-candidates.mdの再集計・不足状況節。</t>
         </is>
       </c>
       <c r="R551" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S551" s="2" t="inlineStr">
@@ -40363,7 +40367,7 @@
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>解析元コーパスを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="H558" s="2" t="inlineStr">
@@ -40373,10 +40377,14 @@
       </c>
       <c r="I558" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="J558" s="2" t="inlineStr"/>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01549</t>
+        </is>
+      </c>
       <c r="K558" s="2" t="inlineStr"/>
       <c r="L558" s="2" t="inlineStr"/>
       <c r="M558" s="2" t="inlineStr"/>
@@ -40384,17 +40392,17 @@
       <c r="O558" s="2" t="inlineStr"/>
       <c r="P558" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>解析元を統計学習用ではなく設計パターン抽出元として扱い、A判定21曲と採用曲0曲を分離する方針を記録する。</t>
         </is>
       </c>
       <c r="Q558" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>WBS-001-01549、docs/sound-spec.md、docs/game-boy-music-source-candidates.md。</t>
         </is>
       </c>
       <c r="R558" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S558" s="2" t="inlineStr">
@@ -40447,7 +40455,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J559" s="2" t="inlineStr"/>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01556</t>
+        </is>
+      </c>
       <c r="K559" s="2" t="inlineStr"/>
       <c r="L559" s="2" t="inlineStr">
         <is>
@@ -40461,7 +40473,7 @@
       <c r="Q559" s="2" t="inlineStr"/>
       <c r="R559" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S559" s="2" t="inlineStr">
@@ -41090,7 +41102,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J568" s="2" t="inlineStr"/>
+      <c r="J568" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01557</t>
+        </is>
+      </c>
       <c r="K568" s="2" t="inlineStr"/>
       <c r="L568" s="2" t="inlineStr">
         <is>
@@ -41104,7 +41120,7 @@
       <c r="Q568" s="2" t="inlineStr"/>
       <c r="R568" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S568" s="2" t="inlineStr">
@@ -41157,7 +41173,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J569" s="2" t="inlineStr"/>
+      <c r="J569" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
       <c r="K569" s="2" t="inlineStr"/>
       <c r="L569" s="2" t="inlineStr">
         <is>
@@ -41232,7 +41252,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J570" s="2" t="inlineStr"/>
+      <c r="J570" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01567</t>
+        </is>
+      </c>
       <c r="K570" s="2" t="inlineStr"/>
       <c r="L570" s="2" t="inlineStr"/>
       <c r="M570" s="2" t="inlineStr"/>
@@ -41303,7 +41327,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J571" s="2" t="inlineStr"/>
+      <c r="J571" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01568</t>
+        </is>
+      </c>
       <c r="K571" s="2" t="inlineStr"/>
       <c r="L571" s="2" t="inlineStr"/>
       <c r="M571" s="2" t="inlineStr"/>
@@ -41366,7 +41394,7 @@
       </c>
       <c r="H572" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="I572" s="2" t="inlineStr">
@@ -41374,7 +41402,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J572" s="2" t="inlineStr"/>
+      <c r="J572" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01569</t>
+        </is>
+      </c>
       <c r="K572" s="2" t="inlineStr"/>
       <c r="L572" s="2" t="inlineStr"/>
       <c r="M572" s="2" t="inlineStr"/>
@@ -41382,17 +41414,17 @@
       <c r="O572" s="2" t="inlineStr"/>
       <c r="P572" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が確認対象を実際に確認し、解析結果との一致・不一致と未確認事項を記録する。</t>
         </is>
       </c>
       <c r="Q572" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>人による確認記録、対象曲・対象項目・確認結果。</t>
         </is>
       </c>
       <c r="R572" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S572" s="2" t="inlineStr">
@@ -41445,7 +41477,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J573" s="2" t="inlineStr"/>
+      <c r="J573" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01557, WBS-001-01570</t>
+        </is>
+      </c>
       <c r="K573" s="2" t="inlineStr"/>
       <c r="L573" s="2" t="inlineStr"/>
       <c r="M573" s="2" t="inlineStr"/>
@@ -41455,7 +41491,7 @@
       <c r="Q573" s="2" t="inlineStr"/>
       <c r="R573" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S573" s="2" t="inlineStr">
@@ -41508,7 +41544,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J574" s="2" t="inlineStr"/>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01556</t>
+        </is>
+      </c>
       <c r="K574" s="2" t="inlineStr"/>
       <c r="L574" s="2" t="inlineStr"/>
       <c r="M574" s="2" t="inlineStr"/>
@@ -41579,7 +41619,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J575" s="2" t="inlineStr"/>
+      <c r="J575" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01556</t>
+        </is>
+      </c>
       <c r="K575" s="2" t="inlineStr"/>
       <c r="L575" s="2" t="inlineStr">
         <is>
@@ -41654,7 +41698,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J576" s="2" t="inlineStr"/>
+      <c r="J576" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01570</t>
+        </is>
+      </c>
       <c r="K576" s="2" t="inlineStr"/>
       <c r="L576" s="2" t="inlineStr">
         <is>
@@ -41729,7 +41777,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J577" s="2" t="inlineStr"/>
+      <c r="J577" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01574</t>
+        </is>
+      </c>
       <c r="K577" s="2" t="inlineStr"/>
       <c r="L577" s="2" t="inlineStr"/>
       <c r="M577" s="2" t="inlineStr"/>
@@ -41800,7 +41852,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J578" s="2" t="inlineStr"/>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01574</t>
+        </is>
+      </c>
       <c r="K578" s="2" t="inlineStr"/>
       <c r="L578" s="2" t="inlineStr"/>
       <c r="M578" s="2" t="inlineStr"/>
@@ -41871,7 +41927,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J579" s="2" t="inlineStr"/>
+      <c r="J579" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01575</t>
+        </is>
+      </c>
       <c r="K579" s="2" t="inlineStr"/>
       <c r="L579" s="2" t="inlineStr"/>
       <c r="M579" s="2" t="inlineStr"/>
@@ -41942,7 +42002,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J580" s="2" t="inlineStr"/>
+      <c r="J580" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01571</t>
+        </is>
+      </c>
       <c r="K580" s="2" t="inlineStr"/>
       <c r="L580" s="2" t="inlineStr">
         <is>
@@ -41956,7 +42020,7 @@
       <c r="Q580" s="2" t="inlineStr"/>
       <c r="R580" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S580" s="2" t="inlineStr">
@@ -42009,7 +42073,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J581" s="2" t="inlineStr"/>
+      <c r="J581" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
       <c r="K581" s="2" t="inlineStr"/>
       <c r="L581" s="2" t="inlineStr"/>
       <c r="M581" s="2" t="inlineStr"/>
@@ -42080,7 +42148,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J582" s="2" t="inlineStr"/>
+      <c r="J582" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K582" s="2" t="inlineStr"/>
       <c r="L582" s="2" t="inlineStr"/>
       <c r="M582" s="2" t="inlineStr"/>
@@ -42151,7 +42223,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J583" s="2" t="inlineStr"/>
+      <c r="J583" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K583" s="2" t="inlineStr"/>
       <c r="L583" s="2" t="inlineStr"/>
       <c r="M583" s="2" t="inlineStr"/>
@@ -42222,7 +42298,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K584" s="2" t="inlineStr"/>
       <c r="L584" s="2" t="inlineStr"/>
       <c r="M584" s="2" t="inlineStr"/>
@@ -42293,7 +42373,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J585" s="2" t="inlineStr"/>
+      <c r="J585" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K585" s="2" t="inlineStr"/>
       <c r="L585" s="2" t="inlineStr"/>
       <c r="M585" s="2" t="inlineStr"/>
@@ -42364,7 +42448,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K586" s="2" t="inlineStr"/>
       <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
@@ -42435,7 +42523,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J587" s="2" t="inlineStr"/>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579, WBS-001-01571</t>
+        </is>
+      </c>
       <c r="K587" s="2" t="inlineStr"/>
       <c r="L587" s="2" t="inlineStr">
         <is>
@@ -42510,7 +42602,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
       <c r="K588" s="2" t="inlineStr"/>
       <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
@@ -42520,7 +42616,7 @@
       <c r="Q588" s="2" t="inlineStr"/>
       <c r="R588" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S588" s="2" t="inlineStr">
@@ -42573,7 +42669,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J589" s="2" t="inlineStr"/>
+      <c r="J589" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578, WBS-001-01586</t>
+        </is>
+      </c>
       <c r="K589" s="2" t="inlineStr"/>
       <c r="L589" s="2" t="inlineStr">
         <is>
@@ -42648,7 +42748,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01587</t>
+        </is>
+      </c>
       <c r="K590" s="2" t="inlineStr"/>
       <c r="L590" s="2" t="inlineStr">
         <is>
@@ -42723,7 +42827,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J591" s="2" t="inlineStr"/>
+      <c r="J591" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01588</t>
+        </is>
+      </c>
       <c r="K591" s="2" t="inlineStr"/>
       <c r="L591" s="2" t="inlineStr"/>
       <c r="M591" s="2" t="inlineStr"/>
@@ -42794,7 +42902,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="K592" s="2" t="inlineStr"/>
       <c r="L592" s="2" t="inlineStr"/>
       <c r="M592" s="2" t="inlineStr"/>
@@ -42865,7 +42977,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J593" s="2" t="inlineStr"/>
+      <c r="J593" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01589, WBS-001-01590</t>
+        </is>
+      </c>
       <c r="K593" s="2" t="inlineStr"/>
       <c r="L593" s="2" t="inlineStr">
         <is>
@@ -42940,7 +43056,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J594" s="2" t="inlineStr"/>
+      <c r="J594" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01586</t>
+        </is>
+      </c>
       <c r="K594" s="2" t="inlineStr"/>
       <c r="L594" s="2" t="inlineStr"/>
       <c r="M594" s="2" t="inlineStr"/>
@@ -42950,7 +43070,7 @@
       <c r="Q594" s="2" t="inlineStr"/>
       <c r="R594" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S594" s="2" t="inlineStr">
@@ -43003,7 +43123,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J595" s="2" t="inlineStr"/>
+      <c r="J595" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01591</t>
+        </is>
+      </c>
       <c r="K595" s="2" t="inlineStr"/>
       <c r="L595" s="2" t="inlineStr"/>
       <c r="M595" s="2" t="inlineStr"/>
@@ -43074,7 +43198,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01593</t>
+        </is>
+      </c>
       <c r="K596" s="2" t="inlineStr"/>
       <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
@@ -43082,7 +43210,7 @@
       <c r="O596" s="2" t="inlineStr"/>
       <c r="P596" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が候補曲を試聴し、曲ごとの結果と判断根拠を記録する。</t>
         </is>
       </c>
       <c r="Q596" s="2" t="inlineStr">
@@ -43145,7 +43273,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J597" s="2" t="inlineStr"/>
+      <c r="J597" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01594</t>
+        </is>
+      </c>
       <c r="K597" s="2" t="inlineStr"/>
       <c r="L597" s="2" t="inlineStr">
         <is>
@@ -43157,7 +43289,7 @@
       <c r="O597" s="2" t="inlineStr"/>
       <c r="P597" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>既存仕様と01594の人による試聴結果に照らして、実用候補の有無、問題点、未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q597" s="2" t="inlineStr">
@@ -43220,7 +43352,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="J598" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01595</t>
+        </is>
+      </c>
       <c r="K598" s="2" t="inlineStr"/>
       <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
@@ -43291,7 +43427,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J599" s="2" t="inlineStr"/>
+      <c r="J599" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01595</t>
+        </is>
+      </c>
       <c r="K599" s="2" t="inlineStr"/>
       <c r="L599" s="2" t="inlineStr"/>
       <c r="M599" s="2" t="inlineStr"/>
@@ -43354,7 +43494,7 @@
       </c>
       <c r="H600" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="I600" s="2" t="inlineStr">
@@ -43362,7 +43502,11 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01595, WBS-001-01597</t>
+        </is>
+      </c>
       <c r="K600" s="2" t="inlineStr"/>
       <c r="L600" s="2" t="inlineStr">
         <is>
@@ -43374,17 +43518,17 @@
       <c r="O600" s="2" t="inlineStr"/>
       <c r="P600" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が評価結果を確認し、継続利用の判断と根拠を記録する。</t>
         </is>
       </c>
       <c r="Q600" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>人による継続利用判断、判断根拠、未解決事項。</t>
         </is>
       </c>
       <c r="R600" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S600" s="2" t="inlineStr">
@@ -48795,7 +48939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51301,12 +51445,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01549</t>
+          <t>WBS-001-01558</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -51316,7 +51460,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01528</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -51328,19 +51472,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01549.md</t>
+          <t>wbs/tasks/WBS-001-01558.md</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>CH1～CH4の役割と発音密度を整理する</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -51350,7 +51494,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01525</t>
+          <t>WBS-001-01557</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -51362,19 +51506,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01556.md</t>
+          <t>wbs/tasks/WBS-001-01559.md</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01558</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51396,19 +51540,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01558.md</t>
+          <t>wbs/tasks/WBS-001-01560.md</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01561</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>motifの反復・変奏パターンを整理する</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51430,19 +51574,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01559.md</t>
+          <t>wbs/tasks/WBS-001-01561.md</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01562</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>CH2の伴奏パターンを整理する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51464,19 +51608,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01560.md</t>
+          <t>wbs/tasks/WBS-001-01562.md</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01561</t>
+          <t>WBS-001-01563</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>CH3のベースパターンを整理する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51498,19 +51642,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01561.md</t>
+          <t>wbs/tasks/WBS-001-01563.md</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01562</t>
+          <t>WBS-001-01564</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>CH4のリズムパターンを整理する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51532,19 +51676,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01562.md</t>
+          <t>wbs/tasks/WBS-001-01564.md</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01563</t>
+          <t>WBS-001-01565</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51566,19 +51710,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01563.md</t>
+          <t>wbs/tasks/WBS-001-01565.md</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01564</t>
+          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51588,10 +51732,14 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -51600,19 +51748,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01564.md</t>
+          <t>wbs/tasks/WBS-001-01567.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01565</t>
+          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>解析結果を共通の中間表現へ変換する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51622,10 +51770,14 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01557</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01567</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -51634,19 +51786,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01565.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01567</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>曲・pattern・channel単位の特徴を自動出力する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51659,7 +51811,11 @@
           <t>WBS-001-01566</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01568</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -51668,24 +51824,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01568</t>
+          <t>WBS-001-01570</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -51693,28 +51849,32 @@
           <t>WBS-001-01566</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01569</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が確認対象を実際に確認し、解析結果との一致・不一致と未確認事項を記録する。</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>ハードウェア制約に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51724,10 +51884,14 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr"/>
+          <t>WBS-001-01571</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01556</t>
+        </is>
+      </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -51736,19 +51900,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>一般的な音楽理論に由来するルールを整理する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51758,10 +51922,14 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr"/>
+          <t>WBS-001-01571</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01556</t>
+        </is>
+      </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -51770,19 +51938,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51795,7 +51963,11 @@
           <t>WBS-001-01571</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01570</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -51804,19 +51976,19 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>各ルールに根拠を記録できる形式を決める</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51829,7 +52001,11 @@
           <t>WBS-001-01571</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01574</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -51838,32 +52014,36 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01576</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01571</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01574</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01571</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -51872,32 +52052,36 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01577</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01571</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01575</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01571</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -51906,19 +52090,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -51928,10 +52112,14 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -51940,19 +52128,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01580</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>曲構成とloop構造を生成する</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -51962,10 +52150,14 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -51974,32 +52166,36 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01581</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01579</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01578</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -52008,19 +52204,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52033,7 +52229,11 @@
           <t>WBS-001-01578</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -52042,19 +52242,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52067,7 +52267,11 @@
           <t>WBS-001-01578</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -52076,19 +52280,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52101,7 +52305,11 @@
           <t>WBS-001-01578</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -52110,19 +52318,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52135,7 +52343,11 @@
           <t>WBS-001-01578</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579, WBS-001-01571</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -52144,19 +52356,19 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -52166,10 +52378,14 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>WBS-001-01586</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578, WBS-001-01586</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -52178,19 +52394,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01588</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>hUGEDriver用ASMを生成する</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -52200,10 +52416,14 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr"/>
+          <t>WBS-001-01586</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01587</t>
+        </is>
+      </c>
       <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -52212,19 +52432,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01587</t>
+          <t>WBS-001-01589</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
+          <t>確認用ROMを生成する</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52237,7 +52457,11 @@
           <t>WBS-001-01586</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01588</t>
+        </is>
+      </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -52246,19 +52470,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>hUGEDriver用ASMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52271,7 +52495,11 @@
           <t>WBS-001-01586</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01579</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -52280,19 +52508,19 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -52305,7 +52533,11 @@
           <t>WBS-001-01586</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01589, WBS-001-01590</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -52314,19 +52546,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>複数seedで候補曲を生成する</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -52336,10 +52568,14 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01591</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -52348,53 +52584,57 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01591</t>
+          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
+          <t>人がSameBoyで候補曲を試聴する</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01586</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01593</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が候補曲を試聴し、曲ごとの結果と判断根拠を記録する。</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01593</t>
+          <t>WBS-001-01595</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>複数seedで候補曲を生成する</t>
+          <t>実用候補となるBGMが生成できるか確認する</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -52407,33 +52647,37 @@
           <t>WBS-001-01592</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01594</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>既存仕様と01594の人による試聴結果に照らして、実用候補の有無、問題点、未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01594</t>
+          <t>WBS-001-01596</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
+          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -52441,7 +52685,11 @@
           <t>WBS-001-01592</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01595</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -52450,32 +52698,36 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01597</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01595</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01592</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -52484,24 +52736,24 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -52509,28 +52761,32 @@
           <t>WBS-001-01592</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01595, WBS-001-01597</t>
+        </is>
+      </c>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が評価結果を確認し、継続利用の判断と根拠を記録する。</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -52540,7 +52796,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -52552,19 +52808,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -52574,7 +52830,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
+          <t>WBS-001-01441</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -52586,19 +52842,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52620,19 +52876,19 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -52654,24 +52910,24 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -52688,19 +52944,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52710,7 +52966,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -52722,29 +52978,29 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -52756,19 +53012,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -52790,19 +53046,19 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -52824,19 +53080,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -52858,19 +53114,19 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -52892,19 +53148,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -52926,19 +53182,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -52960,19 +53216,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -52982,7 +53238,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -52994,19 +53250,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53016,7 +53272,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -53028,19 +53284,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53062,19 +53318,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53096,19 +53352,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53130,19 +53386,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53164,19 +53420,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53198,19 +53454,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53232,19 +53488,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53266,19 +53522,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53300,19 +53556,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53334,19 +53590,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53368,19 +53624,19 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -53390,7 +53646,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -53402,29 +53658,29 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -53436,19 +53692,19 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -53458,7 +53714,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -53470,80 +53726,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01661</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01659</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H139"/>
+  <autoFilter ref="A1:H137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53611,7 +53799,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53628,7 +53816,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53645,7 +53833,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7517985611510791</v>
+        <v>0.7553956834532374</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53662,7 +53850,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
@@ -53679,7 +53867,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
@@ -53696,7 +53884,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
@@ -53713,7 +53901,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -54043,19 +54231,19 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8315508021390374</v>
+        <v>0.8368983957219251</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
@@ -74514,7 +74702,7 @@
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルール抽出元として利用できるGame Boy楽曲データを整理する &gt; 利用可能な楽曲数と用途・曲調の偏りを整理する &gt; 利用可能な約20曲を確定し、調査文書とWBSを更新する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルール抽出元として利用できるGame Boy楽曲データを整理する &gt; 利用可能な楽曲数と用途・曲調の偏りを整理する &gt; 解析元コーパスとして利用可能な楽曲を確定し、調査文書とWBSを更新する</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
@@ -74534,7 +74722,7 @@
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F551" s="2" t="inlineStr">
@@ -74773,7 +74961,7 @@
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルール抽出元として利用できるGame Boy楽曲データを整理する &gt; 20曲程度の少数データを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルール抽出元として利用できるGame Boy楽曲データを整理する &gt; 解析元コーパスを統計学習用コーパスではなく設計パターン抽出元として扱う方針を決める</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
@@ -74793,7 +74981,7 @@
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F558" s="2" t="inlineStr">
@@ -75306,7 +75494,7 @@
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -76342,7 +76530,7 @@
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -39896,7 +39896,9 @@
       </c>
       <c r="Q551" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01547、WBS-001-01548、docs/game-boy-music-source-candidates.mdの再集計・不足状況節。</t>
+          <t>WBS-001-01547、WBS-001-01548、docs/game-boy-music-source-candidates.mdの再集計・不足状況節。
+## 方針変更後の位置付け
+完了時点の判断としてA判定21曲を解析元コーパスに確定した履歴は保持する。方針変更後は品質の高い作曲・編曲例や自動作曲ルールの根拠とは扱わず、利用範囲は後続WBSで定義する。</t>
         </is>
       </c>
       <c r="R551" s="2" t="inlineStr">
@@ -40442,7 +40444,7 @@
       </c>
       <c r="G559" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から抽出する設計情報を決める</t>
+          <t>自動作曲ルールの調査対象と根拠の範囲を定義する</t>
         </is>
       </c>
       <c r="H559" s="2" t="inlineStr">
@@ -40513,7 +40515,7 @@
       </c>
       <c r="G560" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>ゲームBGMの構成・loop技法を信頼できる資料から調査する</t>
         </is>
       </c>
       <c r="H560" s="2" t="inlineStr">
@@ -40534,7 +40536,7 @@
       <c r="O560" s="2" t="inlineStr"/>
       <c r="P560" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>資料の出典、適用範囲、Pocket Sweeperへ適用する場合の未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q560" s="2" t="inlineStr">
@@ -40584,7 +40586,7 @@
       </c>
       <c r="G561" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>Game Boy 4chの音源特性と編曲制約を調査する</t>
         </is>
       </c>
       <c r="H561" s="2" t="inlineStr">
@@ -40609,7 +40611,7 @@
       <c r="O561" s="2" t="inlineStr"/>
       <c r="P561" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各制約に出典があり、生成時に検証可能な項目と人の判断が必要な項目を区別する。</t>
         </is>
       </c>
       <c r="Q561" s="2" t="inlineStr">
@@ -40659,7 +40661,7 @@
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>一般音楽理論に基づくmelody・harmony・rhythmの調査を行う</t>
         </is>
       </c>
       <c r="H562" s="2" t="inlineStr">
@@ -40684,7 +40686,7 @@
       <c r="O562" s="2" t="inlineStr"/>
       <c r="P562" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>一般理論の主張ごとに出典、適用条件、Pocket Sweeper向けの未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q562" s="2" t="inlineStr">
@@ -40734,7 +40736,7 @@
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>ゲームBGMにおけるmotif反復・変奏とlayer設計を調査する</t>
         </is>
       </c>
       <c r="H563" s="2" t="inlineStr">
@@ -40755,7 +40757,7 @@
       <c r="O563" s="2" t="inlineStr"/>
       <c r="P563" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>採用候補と未確定事項を出典とともに記録する。</t>
         </is>
       </c>
       <c r="Q563" s="2" t="inlineStr">
@@ -40805,7 +40807,7 @@
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>pulse伴奏・harmonyをGame Boy制約下で設計する条件を調査する</t>
         </is>
       </c>
       <c r="H564" s="2" t="inlineStr">
@@ -40826,7 +40828,7 @@
       <c r="O564" s="2" t="inlineStr"/>
       <c r="P564" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>根拠の種類と適用範囲を記録する。</t>
         </is>
       </c>
       <c r="Q564" s="2" t="inlineStr">
@@ -40876,7 +40878,7 @@
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>wave/bassの役割と音源制約を調査する</t>
         </is>
       </c>
       <c r="H565" s="2" t="inlineStr">
@@ -40897,7 +40899,7 @@
       <c r="O565" s="2" t="inlineStr"/>
       <c r="P565" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>制約と作曲上の選択を分離して記録する。</t>
         </is>
       </c>
       <c r="Q565" s="2" t="inlineStr">
@@ -40947,7 +40949,7 @@
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>CH4 noiseのリズムとゲームBGM向け密度を調査する</t>
         </is>
       </c>
       <c r="H566" s="2" t="inlineStr">
@@ -40968,7 +40970,7 @@
       <c r="O566" s="2" t="inlineStr"/>
       <c r="P566" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>出典と適用条件を記録する。</t>
         </is>
       </c>
       <c r="Q566" s="2" t="inlineStr">
@@ -41018,7 +41020,7 @@
       </c>
       <c r="G567" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>Instrument・effectの実仕様とhUGETracker表現範囲を調査する</t>
         </is>
       </c>
       <c r="H567" s="2" t="inlineStr">
@@ -41039,7 +41041,7 @@
       <c r="O567" s="2" t="inlineStr"/>
       <c r="P567" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>実際に表現可能な項目と自動生成時に検証すべき項目を記録する。</t>
         </is>
       </c>
       <c r="Q567" s="2" t="inlineStr">
@@ -41089,7 +41091,7 @@
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>Game Boy楽曲解析ツールを試作する</t>
+          <t>既存UGE解析機能の現状と不足を棚卸しする</t>
         </is>
       </c>
       <c r="H568" s="2" t="inlineStr">
@@ -41160,7 +41162,7 @@
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>既存analyze_uge.pyが取得できるUGE情報を棚卸しする</t>
         </is>
       </c>
       <c r="H569" s="2" t="inlineStr">
@@ -41173,11 +41175,7 @@
           <t>incomplete</t>
         </is>
       </c>
-      <c r="J569" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
+      <c r="J569" s="2" t="inlineStr"/>
       <c r="K569" s="2" t="inlineStr"/>
       <c r="L569" s="2" t="inlineStr">
         <is>
@@ -41189,7 +41187,7 @@
       <c r="O569" s="2" t="inlineStr"/>
       <c r="P569" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>実装とテストの根拠に基づく棚卸しを記録し、新規実装が必要な項目を限定する。</t>
         </is>
       </c>
       <c r="Q569" s="2" t="inlineStr">
@@ -41239,7 +41237,7 @@
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>生成UGEの検証に必要な解析結果の契約を定義する</t>
         </is>
       </c>
       <c r="H570" s="2" t="inlineStr">
@@ -41264,7 +41262,7 @@
       <c r="O570" s="2" t="inlineStr"/>
       <c r="P570" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>既存結果の再利用可否と、追加が必要な最小項目を記録する。</t>
         </is>
       </c>
       <c r="Q570" s="2" t="inlineStr">
@@ -41314,7 +41312,7 @@
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>自動生成UGEを既存解析機能で機械検証する</t>
         </is>
       </c>
       <c r="H571" s="2" t="inlineStr">
@@ -41339,7 +41337,7 @@
       <c r="O571" s="2" t="inlineStr"/>
       <c r="P571" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>生成入力から期待構造を定義し、既存解析結果との一致を自動テストで確認する。</t>
         </is>
       </c>
       <c r="Q571" s="2" t="inlineStr">
@@ -41531,7 +41529,7 @@
       </c>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>Game Boyハードウェア仕様に由来するルールを定義する</t>
         </is>
       </c>
       <c r="H574" s="2" t="inlineStr">
@@ -41546,7 +41544,7 @@
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="K574" s="2" t="inlineStr"/>
@@ -41556,7 +41554,7 @@
       <c r="O574" s="2" t="inlineStr"/>
       <c r="P574" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>資料・実装の出典と、未確定事項を含むルール定義を記録する。</t>
         </is>
       </c>
       <c r="Q574" s="2" t="inlineStr">
@@ -41606,7 +41604,7 @@
       </c>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>一般音楽理論に由来するルールを定義する</t>
         </is>
       </c>
       <c r="H575" s="2" t="inlineStr">
@@ -41621,7 +41619,7 @@
       </c>
       <c r="J575" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="K575" s="2" t="inlineStr"/>
@@ -41635,7 +41633,7 @@
       <c r="O575" s="2" t="inlineStr"/>
       <c r="P575" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各ルールの根拠・適用範囲・未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q575" s="2" t="inlineStr">
@@ -41685,7 +41683,7 @@
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>既存UGEを形式・回帰テスト用サンプルとして扱う範囲を定義する</t>
         </is>
       </c>
       <c r="H576" s="2" t="inlineStr">
@@ -41700,7 +41698,7 @@
       </c>
       <c r="J576" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="K576" s="2" t="inlineStr"/>
@@ -41714,7 +41712,7 @@
       <c r="O576" s="2" t="inlineStr"/>
       <c r="P576" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>作曲ルールの根拠から明確に除外した利用方針を記録する。</t>
         </is>
       </c>
       <c r="Q576" s="2" t="inlineStr">
@@ -41764,7 +41762,7 @@
       </c>
       <c r="G577" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>作曲ルールの根拠・出典・確度を記録する形式を決める</t>
         </is>
       </c>
       <c r="H577" s="2" t="inlineStr">
@@ -41779,7 +41777,7 @@
       </c>
       <c r="J577" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01572, WBS-001-01573</t>
         </is>
       </c>
       <c r="K577" s="2" t="inlineStr"/>
@@ -41789,7 +41787,7 @@
       <c r="O577" s="2" t="inlineStr"/>
       <c r="P577" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>21曲の統計・多数派を品質根拠として記録できない運用を含め、追跡可能な形式を定義する。</t>
         </is>
       </c>
       <c r="Q577" s="2" t="inlineStr">
@@ -41839,7 +41837,7 @@
       </c>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>melody・motif・rhythm・harmony・bass・noiseを制約付きで管理する方法を決める</t>
         </is>
       </c>
       <c r="H578" s="2" t="inlineStr">
@@ -41854,7 +41852,7 @@
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01573, WBS-001-01572</t>
         </is>
       </c>
       <c r="K578" s="2" t="inlineStr"/>
@@ -41864,7 +41862,7 @@
       <c r="O578" s="2" t="inlineStr"/>
       <c r="P578" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各層の依存関係と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q578" s="2" t="inlineStr">
@@ -41914,7 +41912,7 @@
       </c>
       <c r="G579" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>根拠不足時にルールを追加せず調査へ戻す運用を決める</t>
         </is>
       </c>
       <c r="H579" s="2" t="inlineStr">
@@ -41929,7 +41927,7 @@
       </c>
       <c r="J579" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01575, WBS-001-01576</t>
         </is>
       </c>
       <c r="K579" s="2" t="inlineStr"/>
@@ -41939,7 +41937,7 @@
       <c r="O579" s="2" t="inlineStr"/>
       <c r="P579" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>根拠なしのルール追加を防ぐ判定手順を記録する。</t>
         </is>
       </c>
       <c r="Q579" s="2" t="inlineStr">
@@ -42510,7 +42508,7 @@
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>Game Boy・hUGEDriver・SFX共存制約を生成時に保証する</t>
         </is>
       </c>
       <c r="H587" s="2" t="inlineStr">
@@ -42539,7 +42537,7 @@
       <c r="O587" s="2" t="inlineStr"/>
       <c r="P587" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>Game Boy/hUGEDriver/Pocket Sweeperの実装根拠と試験結果を記録し、未確定の設計選択は残す。</t>
         </is>
       </c>
       <c r="Q587" s="2" t="inlineStr">
@@ -43339,7 +43337,7 @@
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>問題がある場合は生成構造と根拠・試聴結果を分析する</t>
         </is>
       </c>
       <c r="H598" s="2" t="inlineStr">
@@ -43364,7 +43362,7 @@
       <c r="O598" s="2" t="inlineStr"/>
       <c r="P598" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>自動検証・資料根拠・人の試聴を区別して原因と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="Q598" s="2" t="inlineStr">
@@ -51450,7 +51448,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>ゲームBGMの構成・loop技法を信頼できる資料から調査する</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -51467,7 +51465,7 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>資料の出典、適用範囲、Pocket Sweeperへ適用する場合の未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -51484,7 +51482,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CH1～CH4の役割と発音密度を整理する</t>
+          <t>Game Boy 4chの音源特性と編曲制約を調査する</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -51501,7 +51499,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各制約に出典があり、生成時に検証可能な項目と人の判断が必要な項目を区別する。</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -51518,7 +51516,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>一般音楽理論に基づくmelody・harmony・rhythmの調査を行う</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -51535,7 +51533,7 @@
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>一般理論の主張ごとに出典、適用条件、Pocket Sweeper向けの未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -51552,7 +51550,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>motifの反復・変奏パターンを整理する</t>
+          <t>ゲームBGMにおけるmotif反復・変奏とlayer設計を調査する</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -51569,7 +51567,7 @@
       <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>採用候補と未確定事項を出典とともに記録する。</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -51586,7 +51584,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CH2の伴奏パターンを整理する</t>
+          <t>pulse伴奏・harmonyをGame Boy制約下で設計する条件を調査する</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -51603,7 +51601,7 @@
       <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>根拠の種類と適用範囲を記録する。</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -51620,7 +51618,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CH3のベースパターンを整理する</t>
+          <t>wave/bassの役割と音源制約を調査する</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -51637,7 +51635,7 @@
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>制約と作曲上の選択を分離して記録する。</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -51654,7 +51652,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CH4のリズムパターンを整理する</t>
+          <t>CH4 noiseのリズムとゲームBGM向け密度を調査する</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -51671,7 +51669,7 @@
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>出典と適用条件を記録する。</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -51688,7 +51686,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>Instrument・effectの実仕様とhUGETracker表現範囲を調査する</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -51705,7 +51703,7 @@
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>実際に表現可能な項目と自動生成時に検証すべき項目を記録する。</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -51722,7 +51720,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>既存analyze_uge.pyが取得できるUGE情報を棚卸しする</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -51735,15 +51733,11 @@
           <t>WBS-001-01566</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>実装とテストの根拠に基づく棚卸しを記録し、新規実装が必要な項目を限定する。</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -51760,7 +51754,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>解析結果を共通の中間表現へ変換する</t>
+          <t>生成UGEの検証に必要な解析結果の契約を定義する</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -51781,7 +51775,7 @@
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>既存結果の再利用可否と、追加が必要な最小項目を記録する。</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -51798,7 +51792,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>自動生成UGEを既存解析機能で機械検証する</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -51819,7 +51813,7 @@
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>生成入力から期待構造を定義し、既存解析結果との一致を自動テストで確認する。</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -51874,7 +51868,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ハードウェア制約に由来するルールを整理する</t>
+          <t>Game Boyハードウェア仕様に由来するルールを定義する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51889,13 +51883,13 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>資料・実装の出典と、未確定事項を含むルール定義を記録する。</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -51912,7 +51906,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>一般的な音楽理論に由来するルールを整理する</t>
+          <t>一般音楽理論に由来するルールを定義する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51927,13 +51921,13 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01556</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各ルールの根拠・適用範囲・未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -51950,7 +51944,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>既存UGEを形式・回帰テスト用サンプルとして扱う範囲を定義する</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51965,13 +51959,13 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>作曲ルールの根拠から明確に除外した利用方針を記録する。</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -51988,7 +51982,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>各ルールに根拠を記録できる形式を決める</t>
+          <t>作曲ルールの根拠・出典・確度を記録する形式を決める</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -52003,13 +51997,13 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01572, WBS-001-01573</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>21曲の統計・多数派を品質根拠として記録できない運用を含め、追跡可能な形式を定義する。</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -52026,7 +52020,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>melody・motif・rhythm・harmony・bass・noiseを制約付きで管理する方法を決める</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -52041,13 +52035,13 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01573, WBS-001-01572</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>各層の依存関係と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -52064,7 +52058,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>根拠不足時にルールを追加せず調査へ戻す運用を決める</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -52079,13 +52073,13 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01575, WBS-001-01576</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>根拠なしのルール追加を防ぐ判定手順を記録する。</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -52330,7 +52324,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>Game Boy・hUGEDriver・SFX共存制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52351,7 +52345,7 @@
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>Game Boy/hUGEDriver/Pocket Sweeperの実装根拠と試験結果を記録し、未確定の設計選択は残す。</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -52672,7 +52666,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>問題がある場合は生成構造と根拠・試聴結果を分析する</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -52693,7 +52687,7 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>自動検証・資料根拠・人の試聴を区別して原因と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -74998,7 +74992,7 @@
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
@@ -75035,7 +75029,7 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; 曲全体の構成、order、pattern、loop構造を整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; ゲームBGMの構成・loop技法を信頼できる資料から調査する</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
@@ -75072,7 +75066,7 @@
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; CH1～CH4の役割と発音密度を整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; Game Boy 4chの音源特性と編曲制約を調査する</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
@@ -75109,7 +75103,7 @@
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; 音域、音程遷移、note length、休符の使い方を整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; 一般音楽理論に基づくmelody・harmony・rhythmの調査を行う</t>
         </is>
       </c>
       <c r="B562" s="2" t="inlineStr">
@@ -75146,7 +75140,7 @@
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; motifの反復・変奏パターンを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; ゲームBGMにおけるmotif反復・変奏とlayer設計を調査する</t>
         </is>
       </c>
       <c r="B563" s="2" t="inlineStr">
@@ -75183,7 +75177,7 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; CH2の伴奏パターンを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; pulse伴奏・harmonyをGame Boy制約下で設計する条件を調査する</t>
         </is>
       </c>
       <c r="B564" s="2" t="inlineStr">
@@ -75220,7 +75214,7 @@
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; CH3のベースパターンを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; wave/bassの役割と音源制約を調査する</t>
         </is>
       </c>
       <c r="B565" s="2" t="inlineStr">
@@ -75257,7 +75251,7 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; CH4のリズムパターンを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; CH4 noiseのリズムとゲームBGM向け密度を調査する</t>
         </is>
       </c>
       <c r="B566" s="2" t="inlineStr">
@@ -75294,7 +75288,7 @@
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存Game Boy楽曲から抽出する設計情報を決める &gt; Instrument、Wave table、Noise Instrument、effectの使用傾向を整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲ルールの調査対象と根拠の範囲を定義する &gt; Instrument・effectの実仕様とhUGETracker表現範囲を調査する</t>
         </is>
       </c>
       <c r="B567" s="2" t="inlineStr">
@@ -75331,7 +75325,7 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; Game Boy楽曲解析ツールを試作する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存UGE解析機能の現状と不足を棚卸しする</t>
         </is>
       </c>
       <c r="B568" s="2" t="inlineStr">
@@ -75368,7 +75362,7 @@
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; Game Boy楽曲解析ツールを試作する &gt; UGEまたはASMから必要な情報を読み取れることを確認する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存UGE解析機能の現状と不足を棚卸しする &gt; 既存analyze_uge.pyが取得できるUGE情報を棚卸しする</t>
         </is>
       </c>
       <c r="B569" s="2" t="inlineStr">
@@ -75405,7 +75399,7 @@
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; Game Boy楽曲解析ツールを試作する &gt; 解析結果を共通の中間表現へ変換する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存UGE解析機能の現状と不足を棚卸しする &gt; 生成UGEの検証に必要な解析結果の契約を定義する</t>
         </is>
       </c>
       <c r="B570" s="2" t="inlineStr">
@@ -75442,7 +75436,7 @@
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; Game Boy楽曲解析ツールを試作する &gt; 曲・pattern・channel単位の特徴を自動出力する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存UGE解析機能の現状と不足を棚卸しする &gt; 自動生成UGEを既存解析機能で機械検証する</t>
         </is>
       </c>
       <c r="B571" s="2" t="inlineStr">
@@ -75479,7 +75473,7 @@
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; Game Boy楽曲解析ツールを試作する &gt; 少数の既存曲で解析結果を人が確認する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 既存UGE解析機能の現状と不足を棚卸しする &gt; 少数の既存曲で解析結果を人が確認する</t>
         </is>
       </c>
       <c r="B572" s="2" t="inlineStr">
@@ -75553,7 +75547,7 @@
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; ハードウェア制約に由来するルールを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; Game Boyハードウェア仕様に由来するルールを定義する</t>
         </is>
       </c>
       <c r="B574" s="2" t="inlineStr">
@@ -75590,7 +75584,7 @@
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 一般的な音楽理論に由来するルールを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 一般音楽理論に由来するルールを定義する</t>
         </is>
       </c>
       <c r="B575" s="2" t="inlineStr">
@@ -75627,7 +75621,7 @@
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 既存Game Boy楽曲から確認できた設計パターンを整理する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 既存UGEを形式・回帰テスト用サンプルとして扱う範囲を定義する</t>
         </is>
       </c>
       <c r="B576" s="2" t="inlineStr">
@@ -75664,7 +75658,7 @@
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 各ルールに根拠を記録できる形式を決める</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 作曲ルールの根拠・出典・確度を記録する形式を決める</t>
         </is>
       </c>
       <c r="B577" s="2" t="inlineStr">
@@ -75701,7 +75695,7 @@
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; melody motif、rhythm、harmony、bass、noiseのパターンを個別に管理する方法を決める</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; melody・motif・rhythm・harmony・bass・noiseを制約付きで管理する方法を決める</t>
         </is>
       </c>
       <c r="B578" s="2" t="inlineStr">
@@ -75738,7 +75732,7 @@
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; ルール不足時に根拠なく新規ルールを追加しない運用を決める</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; 自動作曲用のルール・パターン表現を決める &gt; 根拠不足時にルールを追加せず調査へ戻す運用を決める</t>
         </is>
       </c>
       <c r="B579" s="2" t="inlineStr">
@@ -76034,7 +76028,7 @@
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルールベースBGM生成ツールを試作する &gt; Game Boy 4chとhUGEDriverの制約を生成時に保証する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルールベースBGM生成ツールを試作する &gt; Game Boy・hUGEDriver・SFX共存制約を生成時に保証する</t>
         </is>
       </c>
       <c r="B587" s="2" t="inlineStr">
@@ -76441,7 +76435,7 @@
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルールベース自動作曲方式の有効性を評価する &gt; 問題がある場合は既存曲との差を解析可能な特徴量で比較する</t>
+          <t>サウンド &gt; BGM制作 &gt; ルールベースによるGame Boy BGM自動生成方式を検証する &gt; ルールベース自動作曲方式の有効性を評価する &gt; 問題がある場合は生成構造と根拠・試聴結果を分析する</t>
         </is>
       </c>
       <c r="B598" s="2" t="inlineStr">

--- a/reports/wbs.xlsx
+++ b/reports/wbs.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'WBS一覧'!$A$1:$S$674</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未完了一覧'!$A$1:$H$136</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'進捗集計'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'検証結果'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'移行対応'!$A$1:$G$674</definedName>
@@ -41172,7 +41172,7 @@
       </c>
       <c r="I569" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="J569" s="2" t="inlineStr"/>
@@ -41182,8 +41182,16 @@
           <t>docs/sound-spec.md, docs/json-format.md</t>
         </is>
       </c>
-      <c r="M569" s="2" t="inlineStr"/>
-      <c r="N569" s="2" t="inlineStr"/>
+      <c r="M569" s="2" t="inlineStr">
+        <is>
+          <t>tools/analyze_uge.py, tests/test_analyze_uge.py</t>
+        </is>
+      </c>
+      <c r="N569" s="2" t="inlineStr">
+        <is>
+          <t>UGE解析機能の取得項目・未対応項目の棚卸し</t>
+        </is>
+      </c>
       <c r="O569" s="2" t="inlineStr"/>
       <c r="P569" s="2" t="inlineStr">
         <is>
@@ -41192,12 +41200,12 @@
       </c>
       <c r="Q569" s="2" t="inlineStr">
         <is>
-          <t>未登録。</t>
+          <t>tools/analyze_uge.py、tests/test_analyze_uge.py、`python3 -m unittest tests.test_analyze_uge`（9件成功）。</t>
         </is>
       </c>
       <c r="R569" s="2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="S569" s="2" t="inlineStr">
@@ -48937,7 +48945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -51715,160 +51723,164 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01568</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>生成UGEの検証に必要な解析結果の契約を定義する</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01567</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>既存analyze_uge.pyが取得できるUGE情報を棚卸しする</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>実装とテストの根拠に基づく棚卸しを記録し、新規実装が必要な項目を限定する。</t>
+          <t>既存結果の再利用可否と、追加が必要な最小項目を記録する。</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01567.md</t>
+          <t>wbs/tasks/WBS-001-01568.md</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01569</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>自動生成UGEを既存解析機能で機械検証する</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01568</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>生成UGEの検証に必要な解析結果の契約を定義する</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01567</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既存結果の再利用可否と、追加が必要な最小項目を記録する。</t>
+          <t>生成入力から期待構造を定義し、既存解析結果との一致を自動テストで確認する。</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01568.md</t>
+          <t>wbs/tasks/WBS-001-01569.md</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01570</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>少数の既存曲で解析結果を人が確認する</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01566</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01569</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>自動生成UGEを既存解析機能で機械検証する</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01566</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01568</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>生成入力から期待構造を定義し、既存解析結果との一致を自動テストで確認する。</t>
+          <t>人が確認対象を実際に確認し、解析結果との一致・不一致と未確認事項を記録する。</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01569.md</t>
+          <t>wbs/tasks/WBS-001-01570.md</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01570</t>
+          <t>WBS-001-01572</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>少数の既存曲で解析結果を人が確認する</t>
+          <t>Game Boyハードウェア仕様に由来するルールを定義する</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01566</t>
+          <t>WBS-001-01571</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01559</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>人が確認対象を実際に確認し、解析結果との一致・不一致と未確認事項を記録する。</t>
+          <t>資料・実装の出典と、未確定事項を含むルール定義を記録する。</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01570.md</t>
+          <t>wbs/tasks/WBS-001-01572.md</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572</t>
+          <t>WBS-001-01573</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Game Boyハードウェア仕様に由来するルールを定義する</t>
+          <t>一般音楽理論に由来するルールを定義する</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -51883,30 +51895,30 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01559</t>
+          <t>WBS-001-01560</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>資料・実装の出典と、未確定事項を含むルール定義を記録する。</t>
+          <t>各ルールの根拠・適用範囲・未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01572.md</t>
+          <t>wbs/tasks/WBS-001-01573.md</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573</t>
+          <t>WBS-001-01574</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>一般音楽理論に由来するルールを定義する</t>
+          <t>既存UGEを形式・回帰テスト用サンプルとして扱う範囲を定義する</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -51921,30 +51933,30 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01560</t>
+          <t>WBS-001-01569</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>各ルールの根拠・適用範囲・未確定事項を記録する。</t>
+          <t>作曲ルールの根拠から明確に除外した利用方針を記録する。</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01573.md</t>
+          <t>wbs/tasks/WBS-001-01574.md</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01574</t>
+          <t>WBS-001-01575</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>既存UGEを形式・回帰テスト用サンプルとして扱う範囲を定義する</t>
+          <t>作曲ルールの根拠・出典・確度を記録する形式を決める</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -51959,30 +51971,30 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01569</t>
+          <t>WBS-001-01572, WBS-001-01573</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>作曲ルールの根拠から明確に除外した利用方針を記録する。</t>
+          <t>21曲の統計・多数派を品質根拠として記録できない運用を含め、追跡可能な形式を定義する。</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01574.md</t>
+          <t>wbs/tasks/WBS-001-01575.md</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575</t>
+          <t>WBS-001-01576</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>作曲ルールの根拠・出典・確度を記録する形式を決める</t>
+          <t>melody・motif・rhythm・harmony・bass・noiseを制約付きで管理する方法を決める</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -51997,30 +52009,30 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01572, WBS-001-01573</t>
+          <t>WBS-001-01573, WBS-001-01572</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>21曲の統計・多数派を品質根拠として記録できない運用を含め、追跡可能な形式を定義する。</t>
+          <t>各層の依存関係と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01575.md</t>
+          <t>wbs/tasks/WBS-001-01576.md</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01576</t>
+          <t>WBS-001-01577</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>melody・motif・rhythm・harmony・bass・noiseを制約付きで管理する方法を決める</t>
+          <t>根拠不足時にルールを追加せず調査へ戻す運用を決める</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -52035,30 +52047,30 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01573, WBS-001-01572</t>
+          <t>WBS-001-01575, WBS-001-01576</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>各層の依存関係と未確定事項を記録する。</t>
+          <t>根拠なしのルール追加を防ぐ判定手順を記録する。</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01576.md</t>
+          <t>wbs/tasks/WBS-001-01577.md</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01577</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>根拠不足時にルールを追加せず調査へ戻す運用を決める</t>
+          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -52068,50 +52080,50 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01571</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01575, WBS-001-01576</t>
+          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>根拠なしのルール追加を防ぐ判定手順を記録する。</t>
+          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01577.md</t>
+          <t>wbs/tasks/WBS-001-01579.md</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01580</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>曲構成とloop構造を生成する</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01578</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01579</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Pythonで再現可能なseed付き生成処理を実装する</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01578</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01578</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
@@ -52122,19 +52134,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01579.md</t>
+          <t>wbs/tasks/WBS-001-01580.md</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01580</t>
+          <t>WBS-001-01581</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>曲構成とloop構造を生成する</t>
+          <t>CH1主旋律をルール・motifパターンから生成する</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -52160,19 +52172,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01580.md</t>
+          <t>wbs/tasks/WBS-001-01581.md</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01581</t>
+          <t>WBS-001-01582</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>CH1主旋律をルール・motifパターンから生成する</t>
+          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -52198,19 +52210,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01581.md</t>
+          <t>wbs/tasks/WBS-001-01582.md</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01582</t>
+          <t>WBS-001-01583</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>CH2伴奏をルール・伴奏パターンから生成する</t>
+          <t>CH3ベースをルール・ベースパターンから生成する</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -52236,19 +52248,19 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01582.md</t>
+          <t>wbs/tasks/WBS-001-01583.md</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01583</t>
+          <t>WBS-001-01584</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CH3ベースをルール・ベースパターンから生成する</t>
+          <t>CH4リズムをルール・Noiseパターンから生成する</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -52274,19 +52286,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01583.md</t>
+          <t>wbs/tasks/WBS-001-01584.md</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01584</t>
+          <t>WBS-001-01585</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CH4リズムをルール・Noiseパターンから生成する</t>
+          <t>Game Boy・hUGEDriver・SFX共存制約を生成時に保証する</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -52301,30 +52313,30 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01579, WBS-001-01571</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>Game Boy/hUGEDriver/Pocket Sweeperの実装根拠と試験結果を記録し、未確定の設計選択は残す。</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01584.md</t>
+          <t>wbs/tasks/WBS-001-01585.md</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01585</t>
+          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Game Boy・hUGEDriver・SFX共存制約を生成時に保証する</t>
+          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -52334,50 +52346,50 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01578</t>
+          <t>WBS-001-01586</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579, WBS-001-01571</t>
+          <t>WBS-001-01578, WBS-001-01586</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>Game Boy/hUGEDriver/Pocket Sweeperの実装根拠と試験結果を記録し、未確定の設計選択は残す。</t>
+          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01585.md</t>
+          <t>wbs/tasks/WBS-001-01587.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01588</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>hUGEDriver用ASMを生成する</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01586</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01587</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>MIDIを経由せず生成結果をGame Boy向け楽曲データへ変換する</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01586</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01578, WBS-001-01586</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
@@ -52388,34 +52400,34 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01587.md</t>
+          <t>wbs/tasks/WBS-001-01588.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01589</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>確認用ROMを生成する</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01586</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01588</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>hUGEDriver用ASMを生成する</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01586</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01587</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
@@ -52426,19 +52438,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01588.md</t>
+          <t>wbs/tasks/WBS-001-01589.md</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01589</t>
+          <t>WBS-001-01590</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>確認用ROMを生成する</t>
+          <t>seedを指定して同一曲を再生成できるようにする</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -52453,7 +52465,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01588</t>
+          <t>WBS-001-01579</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
@@ -52464,19 +52476,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01589.md</t>
+          <t>wbs/tasks/WBS-001-01590.md</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01590</t>
+          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>seedを指定して同一曲を再生成できるようにする</t>
+          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -52491,7 +52503,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01579</t>
+          <t>WBS-001-01589, WBS-001-01590</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
@@ -52502,34 +52514,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01590.md</t>
+          <t>wbs/tasks/WBS-001-01591.md</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01593</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>複数seedで候補曲を生成する</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01591</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>1コマンドで楽曲生成から確認用ROM生成まで実行できるようにする</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01586</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01589, WBS-001-01590</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -52540,133 +52552,133 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01591.md</t>
+          <t>wbs/tasks/WBS-001-01593.md</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01594</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>人がSameBoyで候補曲を試聴する</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01593</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>複数seedで候補曲を生成する</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01592</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01591</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が候補曲を試聴し、曲ごとの結果と判断根拠を記録する。</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01593.md</t>
+          <t>wbs/tasks/WBS-001-01594.md</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01595</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>実用候補となるBGMが生成できるか確認する</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01594</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>人がSameBoyで候補曲を試聴する</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01592</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01593</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>人が候補曲を試聴し、曲ごとの結果と判断根拠を記録する。</t>
+          <t>既存仕様と01594の人による試聴結果に照らして、実用候補の有無、問題点、未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01594.md</t>
+          <t>wbs/tasks/WBS-001-01595.md</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>WBS-001-01596</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>問題がある場合は生成構造と根拠・試聴結果を分析する</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>codex</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>WBS-001-01592</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
           <t>WBS-001-01595</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>実用候補となるBGMが生成できるか確認する</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01592</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01594</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既存仕様と01594の人による試聴結果に照らして、実用候補の有無、問題点、未確定事項を記録する。</t>
+          <t>自動検証・資料根拠・人の試聴を区別して原因と未確定事項を記録する。</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01595.md</t>
+          <t>wbs/tasks/WBS-001-01596.md</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01596</t>
+          <t>WBS-001-01597</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>問題がある場合は生成構造と根拠・試聴結果を分析する</t>
+          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -52687,29 +52699,29 @@
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>自動検証・資料根拠・人の試聴を区別して原因と未確定事項を記録する。</t>
+          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01596.md</t>
+          <t>wbs/tasks/WBS-001-01597.md</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01597</t>
+          <t>WBS-001-01598</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>ルール追加・変更に明確な根拠を持てるか確認する</t>
+          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -52719,68 +52731,64 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01595</t>
+          <t>WBS-001-01595, WBS-001-01597</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
+          <t>人が評価結果を確認し、継続利用の判断と根拠を記録する。</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01597.md</t>
+          <t>wbs/tasks/WBS-001-01598.md</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01598</t>
+          <t>WBS-001-01608</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>今後のGame Boyゲーム開発で継続利用するか判断する</t>
+          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01592</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01595, WBS-001-01597</t>
-        </is>
-      </c>
+          <t>WBS-001-01441</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
       <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>人が評価結果を確認し、継続利用の判断と根拠を記録する。</t>
+          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01598.md</t>
+          <t>wbs/tasks/WBS-001-01608.md</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01608</t>
+          <t>WBS-001-01609</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>初版用タイトルBGMのhUGETracker正本データ `assets/bgm_title.uge` を人が作成・確定する</t>
+          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -52802,19 +52810,19 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01608.md</t>
+          <t>wbs/tasks/WBS-001-01609.md</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01609</t>
+          <t>WBS-001-01610</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>初版用プレイ中BGMのhUGETracker正本データ `assets/bgm_game.uge` を人が作成・確定する</t>
+          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -52836,19 +52844,19 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01609.md</t>
+          <t>wbs/tasks/WBS-001-01610.md</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01610</t>
+          <t>WBS-001-01611</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>初版用クリアBGMのhUGETracker正本データ `assets/bgm_clear.uge` を人が作成・確定する</t>
+          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -52870,24 +52878,24 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01610.md</t>
+          <t>wbs/tasks/WBS-001-01611.md</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01611</t>
+          <t>WBS-001-01612</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>初版用BGM3曲の音色・音量・チャンネル構成の統一性を人が確認する</t>
+          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -52904,29 +52912,29 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01611.md</t>
+          <t>wbs/tasks/WBS-001-01612.md</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01612</t>
+          <t>WBS-001-01616</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>初版BGM3曲をゲームへ組み込み、SameBoyで最終確認する</t>
+          <t>決定効果音を作成する</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01441</t>
+          <t>WBS-001-01613</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -52938,19 +52946,19 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01612.md</t>
+          <t>wbs/tasks/WBS-001-01616.md</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01616</t>
+          <t>WBS-001-01617</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>決定効果音を作成する</t>
+          <t>キャンセル効果音を作成する</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -52972,19 +52980,19 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01616.md</t>
+          <t>wbs/tasks/WBS-001-01617.md</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01617</t>
+          <t>WBS-001-01618</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>キャンセル効果音を作成する</t>
+          <t>マスを開く効果音を作成する</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -53006,19 +53014,19 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01617.md</t>
+          <t>wbs/tasks/WBS-001-01618.md</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01618</t>
+          <t>WBS-001-01619</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>マスを開く効果音を作成する</t>
+          <t>旗を立てる効果音を作成する</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -53040,19 +53048,19 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01618.md</t>
+          <t>wbs/tasks/WBS-001-01619.md</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01619</t>
+          <t>WBS-001-01620</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>旗を立てる効果音を作成する</t>
+          <t>旗を外す効果音を作成する</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -53074,19 +53082,19 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01619.md</t>
+          <t>wbs/tasks/WBS-001-01620.md</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01620</t>
+          <t>WBS-001-01621</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>旗を外す効果音を作成する</t>
+          <t>地雷爆発効果音を作成する</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -53108,19 +53116,19 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01620.md</t>
+          <t>wbs/tasks/WBS-001-01621.md</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01621</t>
+          <t>WBS-001-01622</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>地雷爆発効果音を作成する</t>
+          <t>クリア効果音を作成する</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -53142,19 +53150,19 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01621.md</t>
+          <t>wbs/tasks/WBS-001-01622.md</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01622</t>
+          <t>WBS-001-01623</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>クリア効果音を作成する</t>
+          <t>ゲームオーバー効果音を作成する</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -53176,19 +53184,19 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01622.md</t>
+          <t>wbs/tasks/WBS-001-01623.md</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01623</t>
+          <t>WBS-001-01643</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー効果音を作成する</t>
+          <t>BGM再生開始処理を実装する</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -53198,7 +53206,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01613</t>
+          <t>WBS-001-01624</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -53210,19 +53218,19 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01623.md</t>
+          <t>wbs/tasks/WBS-001-01643.md</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01643</t>
+          <t>WBS-001-01647</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>BGM再生開始処理を実装する</t>
+          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -53244,19 +53252,19 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01643.md</t>
+          <t>wbs/tasks/WBS-001-01647.md</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01647</t>
+          <t>WBS-001-01648</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>CH2 / Pulse2効果音のSFX生成・再生対応を追加する</t>
+          <t>タイトル画面でタイトルBGMを再生する</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -53278,19 +53286,19 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01647.md</t>
+          <t>wbs/tasks/WBS-001-01648.md</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01648</t>
+          <t>WBS-001-01649</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>タイトル画面でタイトルBGMを再生する</t>
+          <t>通常プレイ中にプレイ中BGMを再生する</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -53312,19 +53320,19 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01648.md</t>
+          <t>wbs/tasks/WBS-001-01649.md</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01649</t>
+          <t>WBS-001-01650</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>通常プレイ中にプレイ中BGMを再生する</t>
+          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -53346,19 +53354,19 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01649.md</t>
+          <t>wbs/tasks/WBS-001-01650.md</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01650</t>
+          <t>WBS-001-01652</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>クリア時にクリアBGMまたはクリアジングルを再生する</t>
+          <t>決定操作時に決定効果音を鳴らす</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -53380,19 +53388,19 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01650.md</t>
+          <t>wbs/tasks/WBS-001-01652.md</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01652</t>
+          <t>WBS-001-01653</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>決定操作時に決定効果音を鳴らす</t>
+          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -53414,19 +53422,19 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01652.md</t>
+          <t>wbs/tasks/WBS-001-01653.md</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01653</t>
+          <t>WBS-001-01654</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>キャンセル操作時にキャンセル効果音を鳴らす</t>
+          <t>マスを開いた時にマス開封効果音を鳴らす</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -53448,19 +53456,19 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01653.md</t>
+          <t>wbs/tasks/WBS-001-01654.md</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01654</t>
+          <t>WBS-001-01655</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>マスを開いた時にマス開封効果音を鳴らす</t>
+          <t>旗を立てた時に旗設置効果音を鳴らす</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -53482,19 +53490,19 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01654.md</t>
+          <t>wbs/tasks/WBS-001-01655.md</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01655</t>
+          <t>WBS-001-01656</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>旗を立てた時に旗設置効果音を鳴らす</t>
+          <t>旗を外した時に旗解除効果音を鳴らす</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -53516,19 +53524,19 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01655.md</t>
+          <t>wbs/tasks/WBS-001-01656.md</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01656</t>
+          <t>WBS-001-01657</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>旗を外した時に旗解除効果音を鳴らす</t>
+          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -53550,19 +53558,19 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01656.md</t>
+          <t>wbs/tasks/WBS-001-01657.md</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01657</t>
+          <t>WBS-001-01658</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>地雷を開いた時に地雷爆発効果音を鳴らす</t>
+          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -53584,19 +53592,19 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01657.md</t>
+          <t>wbs/tasks/WBS-001-01658.md</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01658</t>
+          <t>WBS-001-01660</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ゲームオーバー時にゲームオーバー効果音を鳴らす</t>
+          <t>テスト</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -53606,7 +53614,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01624</t>
+          <t>WBS-001-01659</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -53618,24 +53626,24 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01658.md</t>
+          <t>wbs/tasks/WBS-001-01660.md</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01660</t>
+          <t>WBS-001-01661</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>テスト</t>
+          <t>実機確認に使うフラッシュカートの有無を検討する</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>codex</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -53652,29 +53660,29 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01660.md</t>
+          <t>wbs/tasks/WBS-001-01661.md</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01661</t>
+          <t>WBS-001-01664</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>実機確認に使うフラッシュカートの有無を検討する</t>
+          <t>最終版作成</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>codex</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>WBS-001-01659</t>
+          <t>WBS-001-01662</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -53686,46 +53694,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>wbs/tasks/WBS-001-01661.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01664</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>最終版作成</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>codex</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>WBS-001-01662</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>既存項目の作業を完了し、必要な証跡を記録する。</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
           <t>wbs/tasks/WBS-001-01664.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H137"/>
+  <autoFilter ref="A1:H136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53793,7 +53767,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
@@ -53810,7 +53784,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
@@ -53827,7 +53801,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.7553956834532374</v>
+        <v>0.7571942446043165</v>
       </c>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
@@ -53861,7 +53835,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
@@ -54225,16 +54199,16 @@
         <v>374</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.8368983957219251</v>
+        <v>0.839572192513369</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>4</v>
@@ -75382,7 +75356,7 @@
       </c>
       <c r="E569" s="2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="F569" s="2" t="inlineStr">
